--- a/Student Attendance/Class 2/Class 2 - Monthly Attendance - August-2024.xlsx
+++ b/Student Attendance/Class 2/Class 2 - Monthly Attendance - August-2024.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Student Attendance\Class 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9B5B94-4FA3-43CF-B5A0-1DBE81EBD759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB3E432-0456-422F-B3DA-B1F36AA885A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -629,7 +629,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -672,8 +672,8 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -696,18 +696,6 @@
     <xf numFmtId="17" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -723,12 +711,28 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -856,13 +860,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1145,7 +1142,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:AB27"/>
+  <dimension ref="A1:AB26"/>
   <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="1" bestFit="1" customWidth="1"/>
@@ -1175,228 +1172,337 @@
     <col min="29" max="16384" width="3.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="20"/>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+    <row r="1" spans="1:28" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-    </row>
-    <row r="3" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+    </row>
+    <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-    </row>
-    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+    </row>
+    <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B3" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C3" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="str">
-        <f t="shared" ref="F4:V4" si="0">TEXT(F5,"ddd")</f>
+      <c r="F3" s="2" t="str">
+        <f t="shared" ref="F3:V3" si="0">TEXT(F4,"ddd")</f>
         <v>Thu</v>
       </c>
-      <c r="G4" s="2" t="str">
+      <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="H4" s="2" t="str">
+      <c r="H3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="I4" s="2" t="str">
+      <c r="I3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="J4" s="2" t="str">
+      <c r="J3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="K4" s="2" t="str">
+      <c r="K3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="L4" s="2" t="str">
+      <c r="L3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="M4" s="2" t="str">
+      <c r="M3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="N4" s="2" t="str">
+      <c r="N3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="O4" s="2" t="str">
+      <c r="O3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="P4" s="2" t="str">
+      <c r="P3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sun</v>
       </c>
-      <c r="Q4" s="2" t="str">
+      <c r="Q3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Mon</v>
       </c>
-      <c r="R4" s="2" t="str">
+      <c r="R3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Tue</v>
       </c>
-      <c r="S4" s="2" t="str">
+      <c r="S3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Wed</v>
       </c>
-      <c r="T4" s="2" t="str">
+      <c r="T3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Thu</v>
       </c>
-      <c r="U4" s="2" t="str">
+      <c r="U3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Fri</v>
       </c>
-      <c r="V4" s="2" t="str">
+      <c r="V3" s="2" t="str">
         <f t="shared" si="0"/>
         <v>Sat</v>
       </c>
-      <c r="W4" s="24" t="s">
+      <c r="W3" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="X3" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="Y4" s="25" t="s">
+      <c r="Y3" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="Z4" s="26"/>
+      <c r="Z3" s="26"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+    </row>
+    <row r="4" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="19">
+        <v>45519</v>
+      </c>
+      <c r="G4" s="19">
+        <v>45520</v>
+      </c>
+      <c r="H4" s="19">
+        <v>45521</v>
+      </c>
+      <c r="I4" s="19">
+        <v>45522</v>
+      </c>
+      <c r="J4" s="19">
+        <v>45523</v>
+      </c>
+      <c r="K4" s="19">
+        <v>45524</v>
+      </c>
+      <c r="L4" s="19">
+        <v>45525</v>
+      </c>
+      <c r="M4" s="19">
+        <v>45526</v>
+      </c>
+      <c r="N4" s="19">
+        <v>45527</v>
+      </c>
+      <c r="O4" s="19">
+        <v>45528</v>
+      </c>
+      <c r="P4" s="19">
+        <v>45529</v>
+      </c>
+      <c r="Q4" s="19">
+        <v>45530</v>
+      </c>
+      <c r="R4" s="19">
+        <v>45531</v>
+      </c>
+      <c r="S4" s="19">
+        <v>45532</v>
+      </c>
+      <c r="T4" s="19">
+        <v>45533</v>
+      </c>
+      <c r="U4" s="19">
+        <v>45534</v>
+      </c>
+      <c r="V4" s="19">
+        <v>45535</v>
+      </c>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>31</v>
+      </c>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
     </row>
-    <row r="5" spans="1:28" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="19">
-        <v>45519</v>
-      </c>
-      <c r="G5" s="19">
-        <v>45520</v>
-      </c>
-      <c r="H5" s="19">
-        <v>45521</v>
-      </c>
-      <c r="I5" s="19">
-        <v>45522</v>
-      </c>
-      <c r="J5" s="19">
-        <v>45523</v>
-      </c>
-      <c r="K5" s="19">
-        <v>45524</v>
-      </c>
-      <c r="L5" s="19">
-        <v>45525</v>
-      </c>
-      <c r="M5" s="19">
-        <v>45526</v>
-      </c>
-      <c r="N5" s="19">
-        <v>45527</v>
-      </c>
-      <c r="O5" s="19">
-        <v>45528</v>
-      </c>
-      <c r="P5" s="19">
-        <v>45529</v>
-      </c>
-      <c r="Q5" s="19">
-        <v>45530</v>
-      </c>
-      <c r="R5" s="19">
-        <v>45531</v>
-      </c>
-      <c r="S5" s="19">
-        <v>45532</v>
-      </c>
-      <c r="T5" s="19">
-        <v>45533</v>
-      </c>
-      <c r="U5" s="19">
-        <v>45534</v>
-      </c>
-      <c r="V5" s="19">
-        <v>45535</v>
-      </c>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="4" t="s">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12"/>
+      <c r="C5" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q5" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="R5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U5" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="V5" s="9"/>
+      <c r="W5" s="5">
+        <f t="shared" ref="W5:W26" si="1">COUNTIF(F5:V5,"P")</f>
+        <v>4</v>
+      </c>
+      <c r="X5" s="5">
+        <f t="shared" ref="X5:X26" si="2">COUNTIF(F5:V5,"A")</f>
         <v>7</v>
       </c>
-      <c r="Z5" s="5">
-        <v>31</v>
-      </c>
-      <c r="AA5" s="3"/>
+      <c r="Y5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>26</v>
+      </c>
+      <c r="AA5" s="11" t="s">
+        <v>9</v>
+      </c>
       <c r="AB5" s="3"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>117</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="I6" s="28"/>
       <c r="J6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" s="33" t="s">
-        <v>118</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="K6" s="30"/>
       <c r="L6" s="9" t="s">
         <v>37</v>
       </c>
@@ -1409,56 +1515,48 @@
       <c r="O6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P6" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q6" s="33" t="s">
-        <v>119</v>
-      </c>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="30"/>
       <c r="R6" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S6" s="9" t="s">
         <v>36</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U6" s="33" t="s">
-        <v>120</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="U6" s="30"/>
       <c r="V6" s="9"/>
       <c r="W6" s="5">
-        <f>COUNTIF(F6:V6,"P")</f>
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="X6" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z6" s="10">
         <v>4</v>
       </c>
-      <c r="X6" s="5">
-        <f>COUNTIF(F6:V6,"A")</f>
-        <v>7</v>
-      </c>
-      <c r="Y6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>26</v>
-      </c>
-      <c r="AA6" s="11" t="s">
-        <v>9</v>
-      </c>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
     </row>
-    <row r="7" spans="1:28" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -1470,11 +1568,11 @@
       <c r="H7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="32"/>
+      <c r="I7" s="28"/>
       <c r="J7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="34"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="9" t="s">
         <v>37</v>
       </c>
@@ -1484,51 +1582,45 @@
       <c r="N7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="34"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="30"/>
       <c r="R7" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S7" s="9" t="s">
         <v>36</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U7" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="U7" s="30"/>
       <c r="V7" s="9"/>
       <c r="W7" s="5">
-        <f>COUNTIF(F7:V7,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X7" s="5">
-        <f>COUNTIF(F7:V7,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="Y7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>4</v>
-      </c>
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -1540,11 +1632,11 @@
       <c r="H8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="32"/>
+      <c r="I8" s="28"/>
       <c r="J8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="34"/>
+      <c r="K8" s="30"/>
       <c r="L8" s="9" t="s">
         <v>37</v>
       </c>
@@ -1555,8 +1647,8 @@
         <v>37</v>
       </c>
       <c r="O8" s="9"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="34"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="30"/>
       <c r="R8" s="9" t="s">
         <v>36</v>
       </c>
@@ -1564,35 +1656,37 @@
         <v>36</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U8" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="U8" s="30"/>
       <c r="V8" s="9"/>
       <c r="W8" s="5">
-        <f>COUNTIF(F8:V8,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X8" s="5">
-        <f>COUNTIF(F8:V8,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-    </row>
-    <row r="9" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Y8" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z8" s="26"/>
+      <c r="AA8" s="26"/>
+      <c r="AB8" s="27"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" s="12"/>
       <c r="C9" s="7" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -1604,11 +1698,11 @@
       <c r="H9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="32"/>
+      <c r="I9" s="28"/>
       <c r="J9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="34"/>
+      <c r="K9" s="30"/>
       <c r="L9" s="9" t="s">
         <v>37</v>
       </c>
@@ -1619,10 +1713,10 @@
         <v>37</v>
       </c>
       <c r="O9" s="9"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="34"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="30"/>
       <c r="R9" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S9" s="9" t="s">
         <v>36</v>
@@ -1630,35 +1724,41 @@
       <c r="T9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U9" s="34"/>
+      <c r="U9" s="30"/>
       <c r="V9" s="9"/>
       <c r="W9" s="5">
-        <f>COUNTIF(F9:V9,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X9" s="5">
-        <f>COUNTIF(F9:V9,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="Y9" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z9" s="26"/>
-      <c r="AA9" s="26"/>
-      <c r="AB9" s="27"/>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Y9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z9" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA9" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB9" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="9" t="s">
@@ -1670,11 +1770,11 @@
       <c r="H10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="32"/>
+      <c r="I10" s="28"/>
       <c r="J10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="34"/>
+      <c r="K10" s="30"/>
       <c r="L10" s="9" t="s">
         <v>37</v>
       </c>
@@ -1685,52 +1785,55 @@
         <v>37</v>
       </c>
       <c r="O10" s="9"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="34"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="30"/>
       <c r="R10" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S10" s="9" t="s">
         <v>36</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U10" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="U10" s="30"/>
       <c r="V10" s="9"/>
       <c r="W10" s="5">
-        <f>COUNTIF(F10:V10,"P")</f>
-        <v>9</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X10" s="5">
-        <f>COUNTIF(F10:V10,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="Y10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB10" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="Z10" s="10">
+        <f>19*26</f>
+        <v>494</v>
+      </c>
+      <c r="AA10" s="10">
+        <f>21*26</f>
+        <v>546</v>
+      </c>
+      <c r="AB10" s="10">
+        <f>SUM(Z10:AA10)</f>
+        <v>1040</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="7" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="9" t="s">
@@ -1742,11 +1845,11 @@
       <c r="H11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="32"/>
+      <c r="I11" s="28"/>
       <c r="J11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K11" s="34"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="9" t="s">
         <v>37</v>
       </c>
@@ -1757,539 +1860,537 @@
         <v>37</v>
       </c>
       <c r="O11" s="9"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="34"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="30"/>
       <c r="R11" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S11" s="9" t="s">
         <v>36</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U11" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="U11" s="30"/>
       <c r="V11" s="9"/>
       <c r="W11" s="5">
-        <f>COUNTIF(F11:V11,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="X11" s="5">
-        <f>COUNTIF(F11:V11,"A")</f>
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z11" s="10">
+        <f>W6+W7+W8+W11+W12+W13+W15+W19+W20+W21+W22+W23+W24+W25+W26</f>
+        <v>117</v>
+      </c>
+      <c r="AA11" s="10">
+        <f>W5+W9+W10+W14+W16+W17+W18</f>
+        <v>42</v>
+      </c>
+      <c r="AB11" s="10">
+        <f>Z11+AA11</f>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="10">
+        <v>8</v>
+      </c>
+      <c r="B12" s="12"/>
+      <c r="C12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="28"/>
+      <c r="J12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="30"/>
+      <c r="L12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O12" s="9"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="S12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="U12" s="30"/>
+      <c r="V12" s="9"/>
+      <c r="W12" s="5">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="X12" s="5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="Y12" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z12" s="10">
+        <f>Z11/Z10</f>
+        <v>0.23684210526315788</v>
+      </c>
+      <c r="AA12" s="10">
+        <f>AA11/AA10</f>
+        <v>7.6923076923076927E-2</v>
+      </c>
+      <c r="AB12" s="10">
+        <f>AB11/AB10</f>
+        <v>0.1528846153846154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="10">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="28"/>
+      <c r="J13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="30"/>
+      <c r="L13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="9"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="U13" s="30"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="5">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="X13" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15"/>
+      <c r="AB13" s="15"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="28"/>
+      <c r="J14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="30"/>
+      <c r="L14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="9"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="S14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U14" s="30"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="5">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="X14" s="5">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12"/>
+      <c r="C15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="30"/>
+      <c r="L15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="O15" s="9"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="S15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U15" s="30"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="5">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="X15" s="5">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+    </row>
+    <row r="16" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>12</v>
+      </c>
+      <c r="B16" s="12"/>
+      <c r="C16" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="28"/>
+      <c r="J16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="30"/>
+      <c r="L16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O16" s="9"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="T16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="U16" s="30"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="5">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="X16" s="5">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="Y16" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z16" s="26"/>
+      <c r="AA16" s="26"/>
+      <c r="AB16" s="27"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>13</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="28"/>
+      <c r="J17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="30"/>
+      <c r="L17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O17" s="9"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U17" s="30"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="5">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="X17" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="Y17" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z17" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB17" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12"/>
+      <c r="C18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="30"/>
+      <c r="L18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="O18" s="9"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="U18" s="30"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="5">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="X18" s="5">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="Y18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Z11" s="10">
+      <c r="Z18" s="10">
         <f>19*26</f>
         <v>494</v>
       </c>
-      <c r="AA11" s="10">
+      <c r="AA18" s="10">
         <f>21*26</f>
         <v>546</v>
       </c>
-      <c r="AB11" s="10">
-        <f>SUM(Z11:AA11)</f>
+      <c r="AB18" s="10">
+        <f>Z18+AA18</f>
         <v>1040</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
-        <v>7</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I12" s="32"/>
-      <c r="J12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O12" s="9"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U12" s="34"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="5">
-        <f>COUNTIF(F12:V12,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="X12" s="5">
-        <f>COUNTIF(F12:V12,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="Y12" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z12" s="10" t="e">
-        <f>W7+W8+W9+W12+W13+W14+W16+W20+W21+W22+W23+W24+W25+W26+W27+#REF!+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA12" s="10" t="e">
-        <f>W6+W10+W11+W15+W17+W18+W19+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AB12" s="10" t="e">
-        <f>Z12+AA12</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>8</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K13" s="34"/>
-      <c r="L13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O13" s="9"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U13" s="34"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="5">
-        <f>COUNTIF(F13:V13,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="X13" s="5">
-        <f>COUNTIF(F13:V13,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="Y13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z13" s="10" t="e">
-        <f>Z12/Z11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA13" s="10" t="e">
-        <f>AA12/AA11</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AB13" s="10" t="e">
-        <f>AB12/AB11</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
-        <v>9</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="32"/>
-      <c r="J14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="34"/>
-      <c r="L14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O14" s="9"/>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S14" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U14" s="34"/>
-      <c r="V14" s="9"/>
-      <c r="W14" s="5">
-        <f>COUNTIF(F14:V14,"P")</f>
-        <v>8</v>
-      </c>
-      <c r="X14" s="5">
-        <f>COUNTIF(F14:V14,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="15"/>
-      <c r="AA14" s="15"/>
-      <c r="AB14" s="15"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>10</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I15" s="32"/>
-      <c r="J15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" s="9"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U15" s="34"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="5">
-        <f>COUNTIF(F15:V15,"P")</f>
-        <v>5</v>
-      </c>
-      <c r="X15" s="5">
-        <f>COUNTIF(F15:V15,"A")</f>
-        <v>5</v>
-      </c>
-      <c r="Y15" s="17"/>
-      <c r="Z15" s="17"/>
-      <c r="AA15" s="17"/>
-      <c r="AB15" s="17"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
-        <v>11</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K16" s="34"/>
-      <c r="L16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U16" s="34"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="5">
-        <f>COUNTIF(F16:V16,"P")</f>
-        <v>4</v>
-      </c>
-      <c r="X16" s="5">
-        <f>COUNTIF(F16:V16,"A")</f>
-        <v>3</v>
-      </c>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>12</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="32"/>
-      <c r="J17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K17" s="34"/>
-      <c r="L17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="M17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O17" s="9"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U17" s="34"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="5">
-        <f>COUNTIF(F17:V17,"P")</f>
-        <v>8</v>
-      </c>
-      <c r="X17" s="5">
-        <f>COUNTIF(F17:V17,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="Y17" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z17" s="26"/>
-      <c r="AA17" s="26"/>
-      <c r="AB17" s="27"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
-        <v>13</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" s="32"/>
-      <c r="J18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18" s="34"/>
-      <c r="L18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" s="9"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="S18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U18" s="34"/>
-      <c r="V18" s="9"/>
-      <c r="W18" s="5">
-        <f>COUNTIF(F18:V18,"P")</f>
-        <v>5</v>
-      </c>
-      <c r="X18" s="5">
-        <f>COUNTIF(F18:V18,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="Y18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z18" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB18" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>36</v>
       </c>
       <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="32"/>
+      <c r="H19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="28"/>
       <c r="J19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="34"/>
+      <c r="K19" s="30"/>
       <c r="L19" s="9" t="s">
         <v>37</v>
       </c>
@@ -2299,56 +2400,58 @@
       <c r="N19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O19" s="9"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="34"/>
+      <c r="O19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="30"/>
       <c r="R19" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S19" s="9" t="s">
         <v>36</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U19" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="U19" s="30"/>
       <c r="V19" s="9"/>
       <c r="W19" s="5">
-        <f>COUNTIF(F19:V19,"P")</f>
-        <v>4</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X19" s="5">
-        <f>COUNTIF(F19:V19,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="Y19" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Z19" s="10">
-        <f>19*26</f>
-        <v>494</v>
+        <f>Z18-Z11</f>
+        <v>377</v>
       </c>
       <c r="AA19" s="10">
-        <f>21*26</f>
-        <v>546</v>
+        <f>AA18-AA11</f>
+        <v>504</v>
       </c>
       <c r="AB19" s="10">
         <f>Z19+AA19</f>
-        <v>1040</v>
+        <v>881</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E20" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F20" s="9" t="s">
@@ -2358,11 +2461,11 @@
       <c r="H20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="32"/>
+      <c r="I20" s="28"/>
       <c r="J20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="34"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="9" t="s">
         <v>37</v>
       </c>
@@ -2373,12 +2476,12 @@
         <v>37</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="30"/>
       <c r="R20" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S20" s="9" t="s">
         <v>36</v>
@@ -2386,44 +2489,44 @@
       <c r="T20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U20" s="34"/>
+      <c r="U20" s="30"/>
       <c r="V20" s="9"/>
       <c r="W20" s="5">
-        <f>COUNTIF(F20:V20,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="X20" s="5">
-        <f>COUNTIF(F20:V20,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="Y20" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z20" s="10" t="e">
-        <f>Z19-Z12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA20" s="10" t="e">
-        <f>AA19-AA12</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AB20" s="10" t="e">
-        <f>Z20+AA20</f>
-        <v>#REF!</v>
+        <v>15</v>
+      </c>
+      <c r="Z20" s="18">
+        <f>Z19/Z18</f>
+        <v>0.76315789473684215</v>
+      </c>
+      <c r="AA20" s="18">
+        <f>AA19/AA18</f>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="AB20" s="18">
+        <f>AB19/AB18</f>
+        <v>0.8471153846153846</v>
       </c>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21" s="12"/>
       <c r="C21" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F21" s="9" t="s">
@@ -2433,11 +2536,11 @@
       <c r="H21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I21" s="32"/>
+      <c r="I21" s="28"/>
       <c r="J21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="34"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="9" t="s">
         <v>37</v>
       </c>
@@ -2448,12 +2551,12 @@
         <v>37</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S21" s="9" t="s">
         <v>36</v>
@@ -2461,58 +2564,41 @@
       <c r="T21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U21" s="34"/>
+      <c r="U21" s="30"/>
       <c r="V21" s="9"/>
       <c r="W21" s="5">
-        <f>COUNTIF(F21:V21,"P")</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X21" s="5">
-        <f>COUNTIF(F21:V21,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="Y21" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z21" s="18" t="e">
-        <f>Z20/Z19</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AA21" s="18" t="e">
-        <f>AA20/AA19</f>
-        <v>#REF!</v>
-      </c>
-      <c r="AB21" s="18" t="e">
-        <f>AB20/AB19</f>
-        <v>#REF!</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" s="12"/>
       <c r="C22" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="9" t="s">
-        <v>36</v>
-      </c>
+      <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="32"/>
+      <c r="I22" s="28"/>
       <c r="J22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="34"/>
+      <c r="K22" s="30"/>
       <c r="L22" s="9" t="s">
         <v>37</v>
       </c>
@@ -2523,10 +2609,10 @@
         <v>37</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="P22" s="28"/>
+      <c r="Q22" s="30"/>
       <c r="R22" s="9" t="s">
         <v>37</v>
       </c>
@@ -2536,46 +2622,50 @@
       <c r="T22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U22" s="34"/>
+      <c r="U22" s="30"/>
       <c r="V22" s="9"/>
       <c r="W22" s="5">
-        <f>COUNTIF(F22:V22,"P")</f>
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="X22" s="5">
-        <f>COUNTIF(F22:V22,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" s="12"/>
       <c r="C23" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="F23" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>37</v>
+      </c>
       <c r="H23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="32"/>
+      <c r="I23" s="28"/>
       <c r="J23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="34"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="9" t="s">
         <v>37</v>
       </c>
       <c r="M23" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N23" s="9" t="s">
         <v>37</v>
@@ -2583,8 +2673,8 @@
       <c r="O23" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P23" s="32"/>
-      <c r="Q23" s="34"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="30"/>
       <c r="R23" s="9" t="s">
         <v>37</v>
       </c>
@@ -2594,29 +2684,29 @@
       <c r="T23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U23" s="34"/>
+      <c r="U23" s="30"/>
       <c r="V23" s="9"/>
       <c r="W23" s="5">
-        <f>COUNTIF(F23:V23,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="X23" s="5">
-        <f>COUNTIF(F23:V23,"A")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="7" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F24" s="9" t="s">
@@ -2628,61 +2718,61 @@
       <c r="H24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="32"/>
+      <c r="I24" s="28"/>
       <c r="J24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="34"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="9" t="s">
         <v>37</v>
       </c>
       <c r="M24" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N24" s="9" t="s">
         <v>37</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="P24" s="28"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="9" t="s">
         <v>37</v>
       </c>
       <c r="S24" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U24" s="34"/>
+      <c r="U24" s="30"/>
       <c r="V24" s="9"/>
       <c r="W24" s="5">
-        <f>COUNTIF(F24:V24,"P")</f>
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
       <c r="X24" s="5">
-        <f>COUNTIF(F24:V24,"A")</f>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="7" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>37</v>
@@ -2690,11 +2780,11 @@
       <c r="H25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="32"/>
+      <c r="I25" s="28"/>
       <c r="J25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="34"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="9" t="s">
         <v>37</v>
       </c>
@@ -2704,59 +2794,55 @@
       <c r="N25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O25" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="34"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="30"/>
       <c r="R25" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S25" s="9" t="s">
         <v>37</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U25" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="U25" s="30"/>
       <c r="V25" s="9"/>
       <c r="W25" s="5">
-        <f>COUNTIF(F25:V25,"P")</f>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>8</v>
       </c>
       <c r="X25" s="5">
-        <f>COUNTIF(F25:V25,"A")</f>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B26" s="12"/>
       <c r="C26" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E26" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="20" t="s">
         <v>20</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="9" t="s">
-        <v>37</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G26" s="9"/>
       <c r="H26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I26" s="32"/>
+      <c r="I26" s="28"/>
       <c r="J26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="34"/>
+      <c r="K26" s="31"/>
       <c r="L26" s="9" t="s">
         <v>37</v>
       </c>
@@ -2766,159 +2852,100 @@
       <c r="N26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="O26" s="9"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="34"/>
+      <c r="O26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="31"/>
       <c r="R26" s="9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S26" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="U26" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="U26" s="31"/>
       <c r="V26" s="9"/>
       <c r="W26" s="5">
-        <f>COUNTIF(F26:V26,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X26" s="5">
-        <f>COUNTIF(F26:V26,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
-        <v>22</v>
-      </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="J27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="K27" s="35"/>
-      <c r="L27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="O27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="35"/>
-      <c r="R27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="S27" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T27" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U27" s="35"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="5">
-        <f>COUNTIF(F27:V27,"P")</f>
-        <v>8</v>
-      </c>
-      <c r="X27" s="5">
-        <f>COUNTIF(F27:V27,"A")</f>
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="I6:I27"/>
-    <mergeCell ref="P6:P27"/>
-    <mergeCell ref="K6:K27"/>
-    <mergeCell ref="Q6:Q27"/>
-    <mergeCell ref="U6:U27"/>
-    <mergeCell ref="W4:W5"/>
-    <mergeCell ref="X4:X5"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="Y17:AB17"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
+  <mergeCells count="17">
+    <mergeCell ref="I5:I26"/>
+    <mergeCell ref="P5:P26"/>
+    <mergeCell ref="K5:K26"/>
+    <mergeCell ref="Q5:Q26"/>
+    <mergeCell ref="U5:U26"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="A1:X1"/>
   </mergeCells>
-  <conditionalFormatting sqref="Y5:Z5 F4:V5 F7:H27 J7:J27 R6:T27 L7:O27 F6:Q6 V6:V27 U6">
-    <cfRule type="expression" dxfId="16" priority="15">
-      <formula>F$4="Sun"</formula>
+  <conditionalFormatting sqref="F5:Q5 U5 R5:T26 V5:V26 F6:H26 J6:J26 L6:O26 F4:V4">
+    <cfRule type="expression" dxfId="16" priority="14">
+      <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:V5 F7:H27 J7:J27 R6:T27 L7:O27 F6:Q6 V6:V27 U6">
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>IF(F$5=TODAY(),TRUE,FALSE)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:H27 J7:J27 R6:T27 L7:O27 F6:Q6 V6:V27 U6">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+  <conditionalFormatting sqref="F5:Q5 U5 R5:T26 V5:V26 F6:H26 J6:J26 L6:O26">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="3" operator="equal">
       <formula>"P"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W4:X4 W6:X27">
+  <conditionalFormatting sqref="F3:V4 F5:Q5 U5 R5:T26 V5:V26 F6:H26 J6:J26 L6:O26 Y4:Z4">
+    <cfRule type="expression" dxfId="12" priority="15">
+      <formula>F$3="Sun"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W3:X3 W5:X26">
     <cfRule type="expression" dxfId="11" priority="16">
       <formula>#REF!="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y6:Y7">
+  <conditionalFormatting sqref="Y5:Y6">
     <cfRule type="expression" dxfId="10" priority="12">
-      <formula>Y$4="Sun"</formula>
+      <formula>Y$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y10:Y13">
+  <conditionalFormatting sqref="Y9:Y12">
     <cfRule type="expression" dxfId="9" priority="6">
-      <formula>Y$4="Sun"</formula>
+      <formula>Y$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y18:Y21">
+  <conditionalFormatting sqref="Y17:Y20">
     <cfRule type="expression" dxfId="8" priority="5">
-      <formula>Y$4="Sun"</formula>
+      <formula>Y$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z10:AB10">
+  <conditionalFormatting sqref="Z9:AB9">
     <cfRule type="expression" dxfId="7" priority="7">
-      <formula>Z$4="Sun"</formula>
+      <formula>Z$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z18:AB18">
+  <conditionalFormatting sqref="Z17:AB17">
     <cfRule type="expression" dxfId="6" priority="4">
-      <formula>Z$4="Sun"</formula>
+      <formula>Z$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2990,32 +3017,32 @@
       <c r="X1" s="21"/>
     </row>
     <row r="2" spans="1:28" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="36"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="36"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
     </row>
     <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -3205,13 +3232,13 @@
       <c r="H5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="I5" s="33" t="s">
         <v>116</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="33" t="s">
+      <c r="K5" s="29" t="s">
         <v>118</v>
       </c>
       <c r="L5" s="9" t="s">
@@ -3226,10 +3253,10 @@
       <c r="O5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P5" s="28" t="s">
+      <c r="P5" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="Q5" s="33" t="s">
+      <c r="Q5" s="29" t="s">
         <v>119</v>
       </c>
       <c r="R5" s="9" t="s">
@@ -3241,16 +3268,16 @@
       <c r="T5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U5" s="33" t="s">
+      <c r="U5" s="29" t="s">
         <v>120</v>
       </c>
       <c r="V5" s="9"/>
       <c r="W5" s="5">
-        <f>COUNTIF(F5:V5,"P")</f>
+        <f t="shared" ref="W5:W30" si="1">COUNTIF(F5:V5,"P")</f>
         <v>11</v>
       </c>
       <c r="X5" s="5">
-        <f>COUNTIF(F5:V5,"A")</f>
+        <f t="shared" ref="X5:X30" si="2">COUNTIF(F5:V5,"A")</f>
         <v>0</v>
       </c>
       <c r="Y5" s="5" t="s">
@@ -3287,11 +3314,11 @@
       <c r="H6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="29"/>
+      <c r="I6" s="34"/>
       <c r="J6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K6" s="34"/>
+      <c r="K6" s="30"/>
       <c r="L6" s="9" t="s">
         <v>37</v>
       </c>
@@ -3304,8 +3331,8 @@
       <c r="O6" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="30"/>
       <c r="R6" s="9" t="s">
         <v>37</v>
       </c>
@@ -3315,14 +3342,14 @@
       <c r="T6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U6" s="34"/>
+      <c r="U6" s="30"/>
       <c r="V6" s="9"/>
       <c r="W6" s="5">
-        <f>COUNTIF(F6:V6,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X6" s="5">
-        <f>COUNTIF(F6:V6,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y6" s="5" t="s">
@@ -3357,11 +3384,11 @@
       <c r="H7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="29"/>
+      <c r="I7" s="34"/>
       <c r="J7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K7" s="34"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="9" t="s">
         <v>37</v>
       </c>
@@ -3374,8 +3401,8 @@
       <c r="O7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="30"/>
       <c r="R7" s="9" t="s">
         <v>37</v>
       </c>
@@ -3385,14 +3412,14 @@
       <c r="T7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U7" s="34"/>
+      <c r="U7" s="30"/>
       <c r="V7" s="9"/>
       <c r="W7" s="5">
-        <f>COUNTIF(F7:V7,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X7" s="5">
-        <f>COUNTIF(F7:V7,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y7" s="3"/>
@@ -3423,11 +3450,11 @@
       <c r="H8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="29"/>
+      <c r="I8" s="34"/>
       <c r="J8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="34"/>
+      <c r="K8" s="30"/>
       <c r="L8" s="9" t="s">
         <v>37</v>
       </c>
@@ -3440,8 +3467,8 @@
       <c r="O8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="30"/>
       <c r="R8" s="9" t="s">
         <v>37</v>
       </c>
@@ -3451,14 +3478,14 @@
       <c r="T8" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U8" s="34"/>
+      <c r="U8" s="30"/>
       <c r="V8" s="9"/>
       <c r="W8" s="5">
-        <f>COUNTIF(F8:V8,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="X8" s="5">
-        <f>COUNTIF(F8:V8,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y8" s="25" t="s">
@@ -3491,11 +3518,11 @@
       <c r="H9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="29"/>
+      <c r="I9" s="34"/>
       <c r="J9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="34"/>
+      <c r="K9" s="30"/>
       <c r="L9" s="9" t="s">
         <v>37</v>
       </c>
@@ -3508,8 +3535,8 @@
       <c r="O9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="30"/>
       <c r="R9" s="9" t="s">
         <v>36</v>
       </c>
@@ -3519,14 +3546,14 @@
       <c r="T9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U9" s="34"/>
+      <c r="U9" s="30"/>
       <c r="V9" s="9"/>
       <c r="W9" s="5">
-        <f>COUNTIF(F9:V9,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="X9" s="5">
-        <f>COUNTIF(F9:V9,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="Y9" s="5" t="s">
@@ -3565,11 +3592,11 @@
       <c r="H10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="29"/>
+      <c r="I10" s="34"/>
       <c r="J10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="34"/>
+      <c r="K10" s="30"/>
       <c r="L10" s="9" t="s">
         <v>37</v>
       </c>
@@ -3582,8 +3609,8 @@
       <c r="O10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="30"/>
       <c r="R10" s="9" t="s">
         <v>37</v>
       </c>
@@ -3593,14 +3620,14 @@
       <c r="T10" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U10" s="34"/>
+      <c r="U10" s="30"/>
       <c r="V10" s="9"/>
       <c r="W10" s="5">
-        <f>COUNTIF(F10:V10,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="X10" s="5">
-        <f>COUNTIF(F10:V10,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="Y10" s="5" t="s">
@@ -3642,11 +3669,11 @@
       <c r="H11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="29"/>
+      <c r="I11" s="34"/>
       <c r="J11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K11" s="34"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="9" t="s">
         <v>37</v>
       </c>
@@ -3659,8 +3686,8 @@
       <c r="O11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="30"/>
       <c r="R11" s="9" t="s">
         <v>36</v>
       </c>
@@ -3670,14 +3697,14 @@
       <c r="T11" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U11" s="34"/>
+      <c r="U11" s="30"/>
       <c r="V11" s="9"/>
       <c r="W11" s="5">
-        <f>COUNTIF(F11:V11,"P")</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="X11" s="5">
-        <f>COUNTIF(F11:V11,"A")</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="Y11" s="5" t="s">
@@ -3719,11 +3746,11 @@
       <c r="H12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I12" s="29"/>
+      <c r="I12" s="34"/>
       <c r="J12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K12" s="34"/>
+      <c r="K12" s="30"/>
       <c r="L12" s="9" t="s">
         <v>37</v>
       </c>
@@ -3736,8 +3763,8 @@
       <c r="O12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="30"/>
       <c r="R12" s="9" t="s">
         <v>37</v>
       </c>
@@ -3747,14 +3774,14 @@
       <c r="T12" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U12" s="34"/>
+      <c r="U12" s="30"/>
       <c r="V12" s="9"/>
       <c r="W12" s="5">
-        <f>COUNTIF(F12:V12,"P")</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="X12" s="5">
-        <f>COUNTIF(F12:V12,"A")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Y12" s="5" t="s">
@@ -3796,11 +3823,11 @@
       <c r="H13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I13" s="29"/>
+      <c r="I13" s="34"/>
       <c r="J13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K13" s="34"/>
+      <c r="K13" s="30"/>
       <c r="L13" s="9" t="s">
         <v>37</v>
       </c>
@@ -3813,8 +3840,8 @@
       <c r="O13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="29"/>
-      <c r="Q13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="30"/>
       <c r="R13" s="9" t="s">
         <v>36</v>
       </c>
@@ -3824,14 +3851,14 @@
       <c r="T13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U13" s="34"/>
+      <c r="U13" s="30"/>
       <c r="V13" s="9"/>
       <c r="W13" s="5">
-        <f>COUNTIF(F13:V13,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X13" s="5">
-        <f>COUNTIF(F13:V13,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y13" s="3"/>
@@ -3862,11 +3889,11 @@
       <c r="H14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="29"/>
+      <c r="I14" s="34"/>
       <c r="J14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="34"/>
+      <c r="K14" s="30"/>
       <c r="L14" s="9" t="s">
         <v>37</v>
       </c>
@@ -3879,8 +3906,8 @@
       <c r="O14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="30"/>
       <c r="R14" s="9" t="s">
         <v>37</v>
       </c>
@@ -3888,14 +3915,14 @@
       <c r="T14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U14" s="34"/>
+      <c r="U14" s="30"/>
       <c r="V14" s="9"/>
       <c r="W14" s="5">
-        <f>COUNTIF(F14:V14,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="X14" s="5">
-        <f>COUNTIF(F14:V14,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y14" s="17"/>
@@ -3926,11 +3953,11 @@
       <c r="H15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="29"/>
+      <c r="I15" s="34"/>
       <c r="J15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K15" s="34"/>
+      <c r="K15" s="30"/>
       <c r="L15" s="9" t="s">
         <v>37</v>
       </c>
@@ -3943,8 +3970,8 @@
       <c r="O15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P15" s="29"/>
-      <c r="Q15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="30"/>
       <c r="R15" s="9" t="s">
         <v>37</v>
       </c>
@@ -3954,14 +3981,14 @@
       <c r="T15" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U15" s="34"/>
+      <c r="U15" s="30"/>
       <c r="V15" s="9"/>
       <c r="W15" s="5">
-        <f>COUNTIF(F15:V15,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X15" s="5">
-        <f>COUNTIF(F15:V15,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y15" s="3"/>
@@ -3992,11 +4019,11 @@
       <c r="H16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I16" s="29"/>
+      <c r="I16" s="34"/>
       <c r="J16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="34"/>
+      <c r="K16" s="30"/>
       <c r="L16" s="9" t="s">
         <v>37</v>
       </c>
@@ -4009,8 +4036,8 @@
       <c r="O16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="30"/>
       <c r="R16" s="9" t="s">
         <v>36</v>
       </c>
@@ -4020,14 +4047,14 @@
       <c r="T16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U16" s="34"/>
+      <c r="U16" s="30"/>
       <c r="V16" s="9"/>
       <c r="W16" s="5">
-        <f>COUNTIF(F16:V16,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X16" s="5">
-        <f>COUNTIF(F16:V16,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y16" s="25" t="s">
@@ -4060,11 +4087,11 @@
       <c r="H17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I17" s="29"/>
+      <c r="I17" s="34"/>
       <c r="J17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="34"/>
+      <c r="K17" s="30"/>
       <c r="L17" s="9" t="s">
         <v>37</v>
       </c>
@@ -4077,8 +4104,8 @@
       <c r="O17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P17" s="29"/>
-      <c r="Q17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="30"/>
       <c r="R17" s="9" t="s">
         <v>36</v>
       </c>
@@ -4088,14 +4115,14 @@
       <c r="T17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U17" s="34"/>
+      <c r="U17" s="30"/>
       <c r="V17" s="9"/>
       <c r="W17" s="5">
-        <f>COUNTIF(F17:V17,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X17" s="5">
-        <f>COUNTIF(F17:V17,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y17" s="5" t="s">
@@ -4134,11 +4161,11 @@
       <c r="H18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I18" s="29"/>
+      <c r="I18" s="34"/>
       <c r="J18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K18" s="34"/>
+      <c r="K18" s="30"/>
       <c r="L18" s="9" t="s">
         <v>37</v>
       </c>
@@ -4151,8 +4178,8 @@
       <c r="O18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P18" s="29"/>
-      <c r="Q18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="30"/>
       <c r="R18" s="9" t="s">
         <v>37</v>
       </c>
@@ -4162,14 +4189,14 @@
       <c r="T18" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U18" s="34"/>
+      <c r="U18" s="30"/>
       <c r="V18" s="9"/>
       <c r="W18" s="5">
-        <f>COUNTIF(F18:V18,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X18" s="5">
-        <f>COUNTIF(F18:V18,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y18" s="5" t="s">
@@ -4211,11 +4238,11 @@
       <c r="H19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I19" s="29"/>
+      <c r="I19" s="34"/>
       <c r="J19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K19" s="34"/>
+      <c r="K19" s="30"/>
       <c r="L19" s="9" t="s">
         <v>37</v>
       </c>
@@ -4228,8 +4255,8 @@
       <c r="O19" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="30"/>
       <c r="R19" s="9" t="s">
         <v>37</v>
       </c>
@@ -4239,14 +4266,14 @@
       <c r="T19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U19" s="34"/>
+      <c r="U19" s="30"/>
       <c r="V19" s="9"/>
       <c r="W19" s="5">
-        <f>COUNTIF(F19:V19,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X19" s="5">
-        <f>COUNTIF(F19:V19,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="Y19" s="5" t="s">
@@ -4288,11 +4315,11 @@
       <c r="H20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I20" s="29"/>
+      <c r="I20" s="34"/>
       <c r="J20" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K20" s="34"/>
+      <c r="K20" s="30"/>
       <c r="L20" s="9" t="s">
         <v>37</v>
       </c>
@@ -4305,8 +4332,8 @@
       <c r="O20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="30"/>
       <c r="R20" s="9" t="s">
         <v>37</v>
       </c>
@@ -4316,14 +4343,14 @@
       <c r="T20" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U20" s="34"/>
+      <c r="U20" s="30"/>
       <c r="V20" s="9"/>
       <c r="W20" s="5">
-        <f>COUNTIF(F20:V20,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X20" s="5">
-        <f>COUNTIF(F20:V20,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Y20" s="5" t="s">
@@ -4365,11 +4392,11 @@
       <c r="H21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I21" s="29"/>
+      <c r="I21" s="34"/>
       <c r="J21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K21" s="34"/>
+      <c r="K21" s="30"/>
       <c r="L21" s="9" t="s">
         <v>37</v>
       </c>
@@ -4382,8 +4409,8 @@
       <c r="O21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P21" s="29"/>
-      <c r="Q21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="30"/>
       <c r="R21" s="9" t="s">
         <v>37</v>
       </c>
@@ -4393,14 +4420,14 @@
       <c r="T21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U21" s="34"/>
+      <c r="U21" s="30"/>
       <c r="V21" s="9"/>
       <c r="W21" s="5">
-        <f>COUNTIF(F21:V21,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="X21" s="5">
-        <f>COUNTIF(F21:V21,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4427,11 +4454,11 @@
       <c r="H22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I22" s="29"/>
+      <c r="I22" s="34"/>
       <c r="J22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K22" s="34"/>
+      <c r="K22" s="30"/>
       <c r="L22" s="9" t="s">
         <v>37</v>
       </c>
@@ -4444,8 +4471,8 @@
       <c r="O22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P22" s="29"/>
-      <c r="Q22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="30"/>
       <c r="R22" s="9" t="s">
         <v>36</v>
       </c>
@@ -4455,14 +4482,14 @@
       <c r="T22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U22" s="34"/>
+      <c r="U22" s="30"/>
       <c r="V22" s="9"/>
       <c r="W22" s="5">
-        <f>COUNTIF(F22:V22,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X22" s="5">
-        <f>COUNTIF(F22:V22,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -4489,11 +4516,11 @@
       <c r="H23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I23" s="29"/>
+      <c r="I23" s="34"/>
       <c r="J23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K23" s="34"/>
+      <c r="K23" s="30"/>
       <c r="L23" s="9" t="s">
         <v>37</v>
       </c>
@@ -4506,8 +4533,8 @@
       <c r="O23" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="30"/>
       <c r="R23" s="9" t="s">
         <v>36</v>
       </c>
@@ -4517,14 +4544,14 @@
       <c r="T23" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U23" s="34"/>
+      <c r="U23" s="30"/>
       <c r="V23" s="9"/>
       <c r="W23" s="5">
-        <f>COUNTIF(F23:V23,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X23" s="5">
-        <f>COUNTIF(F23:V23,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4551,11 +4578,11 @@
       <c r="H24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I24" s="29"/>
+      <c r="I24" s="34"/>
       <c r="J24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K24" s="34"/>
+      <c r="K24" s="30"/>
       <c r="L24" s="9" t="s">
         <v>36</v>
       </c>
@@ -4568,8 +4595,8 @@
       <c r="O24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="30"/>
       <c r="R24" s="9" t="s">
         <v>37</v>
       </c>
@@ -4579,14 +4606,14 @@
       <c r="T24" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U24" s="34"/>
+      <c r="U24" s="30"/>
       <c r="V24" s="9"/>
       <c r="W24" s="5">
-        <f>COUNTIF(F24:V24,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X24" s="5">
-        <f>COUNTIF(F24:V24,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -4613,11 +4640,11 @@
       <c r="H25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I25" s="29"/>
+      <c r="I25" s="34"/>
       <c r="J25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K25" s="34"/>
+      <c r="K25" s="30"/>
       <c r="L25" s="9" t="s">
         <v>37</v>
       </c>
@@ -4630,8 +4657,8 @@
       <c r="O25" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P25" s="29"/>
-      <c r="Q25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="30"/>
       <c r="R25" s="9" t="s">
         <v>36</v>
       </c>
@@ -4641,14 +4668,14 @@
       <c r="T25" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U25" s="34"/>
+      <c r="U25" s="30"/>
       <c r="V25" s="9"/>
       <c r="W25" s="5">
-        <f>COUNTIF(F25:V25,"P")</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="X25" s="5">
-        <f>COUNTIF(F25:V25,"A")</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
     </row>
@@ -4675,11 +4702,11 @@
       <c r="H26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I26" s="29"/>
+      <c r="I26" s="34"/>
       <c r="J26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K26" s="34"/>
+      <c r="K26" s="30"/>
       <c r="L26" s="9" t="s">
         <v>37</v>
       </c>
@@ -4692,8 +4719,8 @@
       <c r="O26" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="30"/>
       <c r="R26" s="9" t="s">
         <v>37</v>
       </c>
@@ -4703,14 +4730,14 @@
       <c r="T26" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U26" s="34"/>
+      <c r="U26" s="30"/>
       <c r="V26" s="9"/>
       <c r="W26" s="5">
-        <f>COUNTIF(F26:V26,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X26" s="5">
-        <f>COUNTIF(F26:V26,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4737,11 +4764,11 @@
       <c r="H27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I27" s="29"/>
+      <c r="I27" s="34"/>
       <c r="J27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K27" s="34"/>
+      <c r="K27" s="30"/>
       <c r="L27" s="9" t="s">
         <v>36</v>
       </c>
@@ -4754,8 +4781,8 @@
       <c r="O27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="30"/>
       <c r="R27" s="9" t="s">
         <v>37</v>
       </c>
@@ -4765,14 +4792,14 @@
       <c r="T27" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="U27" s="34"/>
+      <c r="U27" s="30"/>
       <c r="V27" s="9"/>
       <c r="W27" s="5">
-        <f>COUNTIF(F27:V27,"P")</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="X27" s="5">
-        <f>COUNTIF(F27:V27,"A")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -4799,11 +4826,11 @@
       <c r="H28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I28" s="29"/>
+      <c r="I28" s="34"/>
       <c r="J28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K28" s="34"/>
+      <c r="K28" s="30"/>
       <c r="L28" s="9" t="s">
         <v>37</v>
       </c>
@@ -4816,8 +4843,8 @@
       <c r="O28" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P28" s="29"/>
-      <c r="Q28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="30"/>
       <c r="R28" s="9" t="s">
         <v>37</v>
       </c>
@@ -4827,14 +4854,14 @@
       <c r="T28" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U28" s="34"/>
+      <c r="U28" s="30"/>
       <c r="V28" s="9"/>
       <c r="W28" s="5">
-        <f>COUNTIF(F28:V28,"P")</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="X28" s="5">
-        <f>COUNTIF(F28:V28,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -4861,11 +4888,11 @@
       <c r="H29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I29" s="29"/>
+      <c r="I29" s="34"/>
       <c r="J29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="K29" s="34"/>
+      <c r="K29" s="30"/>
       <c r="L29" s="9" t="s">
         <v>37</v>
       </c>
@@ -4878,8 +4905,8 @@
       <c r="O29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="30"/>
       <c r="R29" s="9" t="s">
         <v>37</v>
       </c>
@@ -4889,14 +4916,14 @@
       <c r="T29" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U29" s="34"/>
+      <c r="U29" s="30"/>
       <c r="V29" s="9"/>
       <c r="W29" s="5">
-        <f>COUNTIF(F29:V29,"P")</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="X29" s="5">
-        <f>COUNTIF(F29:V29,"A")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -4917,9 +4944,9 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
-      <c r="I30" s="30"/>
+      <c r="I30" s="35"/>
       <c r="J30" s="9"/>
-      <c r="K30" s="35"/>
+      <c r="K30" s="31"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9" t="s">
@@ -4928,8 +4955,8 @@
       <c r="O30" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="P30" s="30"/>
-      <c r="Q30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="31"/>
       <c r="R30" s="9" t="s">
         <v>37</v>
       </c>
@@ -4939,56 +4966,56 @@
       <c r="T30" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="U30" s="35"/>
+      <c r="U30" s="31"/>
       <c r="V30" s="9"/>
       <c r="W30" s="5">
-        <f>COUNTIF(F30:V30,"P")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="X30" s="5">
-        <f>COUNTIF(F30:V30,"A")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="I5:I30"/>
-    <mergeCell ref="P5:P30"/>
-    <mergeCell ref="K5:K30"/>
-    <mergeCell ref="Q5:Q30"/>
     <mergeCell ref="U5:U30"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="A1:X1"/>
+    <mergeCell ref="A2:X2"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
-    <mergeCell ref="A1:X1"/>
-    <mergeCell ref="A2:X2"/>
-    <mergeCell ref="W3:W4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="I5:I30"/>
+    <mergeCell ref="P5:P30"/>
+    <mergeCell ref="K5:K30"/>
+    <mergeCell ref="Q5:Q30"/>
   </mergeCells>
-  <conditionalFormatting sqref="F3:V4 Y4:Z4 Y5:Y6 Z9:AB9 Y9:Y12 Z17:AB17 Y17:Y20 F6:H30 J6:J30 R5:T30 L6:O30 F5:Q5 V5:V30 U5">
-    <cfRule type="expression" dxfId="5" priority="10">
-      <formula>F$3="Sun"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:V4 F6:H30 J6:J30 R5:T30 L6:O30 F5:Q5 V5:V30 U5">
-    <cfRule type="expression" dxfId="4" priority="9">
+  <conditionalFormatting sqref="F5:Q5 U5 R5:T30 V5:V30 F6:H30 J6:J30 L6:O30 F4:V4">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>IF(F$4=TODAY(),TRUE,FALSE)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F6:H30 J6:J30 R5:T30 L6:O30 F5:Q5 V5:V30 U5">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="F5:Q5 U5 R5:T30 V5:V30 F6:H30 J6:J30 L6:O30">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"P"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:V4 F5:Q5 U5 R5:T30 V5:V30 F6:H30 J6:J30 L6:O30 Y4:Z4 Y5:Y6 Z9:AB9 Y9:Y12 Z17:AB17 Y17:Y20">
+    <cfRule type="expression" dxfId="1" priority="10">
+      <formula>F$3="Sun"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W3:X3 W5:X30">
